--- a/2026_project/1_raw/electricity_price_manual_addition.xlsx
+++ b/2026_project/1_raw/electricity_price_manual_addition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutka\MT\AdOpT-NET0_dw\2026_project\1_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A171700-985A-4521-8E85-DE29DBBBBC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E752034F-A514-4FC6-A139-5E33992BADA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="440" yWindow="4960" windowWidth="21420" windowHeight="7270" xr2:uid="{D2B23FF3-F1F1-467E-B3C6-7887C1546841}"/>
+    <workbookView xWindow="-870" yWindow="3240" windowWidth="25470" windowHeight="9220" xr2:uid="{D2B23FF3-F1F1-467E-B3C6-7887C1546841}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -207,7 +207,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -657,7 +657,7 @@
       <c r="G3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3">
@@ -705,6 +705,7 @@
     <hyperlink ref="H2" r:id="rId1" xr:uid="{06544042-0CC4-4862-8C4E-FEE4B521C61C}"/>
     <hyperlink ref="L2" r:id="rId2" xr:uid="{15F7CF62-D5CB-449A-856F-A3EAA45238B3}"/>
     <hyperlink ref="L3" r:id="rId3" xr:uid="{2E859603-F6A8-4053-A3CF-DEC0E57ADB63}"/>
+    <hyperlink ref="H3" r:id="rId4" xr:uid="{44390380-9332-492A-8247-381615102CD6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
